--- a/assets/docs/E5-Tableau-de-synthese-Mateo.xlsx
+++ b/assets/docs/E5-Tableau-de-synthese-Mateo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\php\Portfolio\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28DE384-E7FD-480C-8009-E8B047B48D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C5D494-7858-400A-B23B-87BC1F422BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="50">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -189,9 +189,6 @@
     <t>x</t>
   </si>
   <si>
-    <t>Sultano, Appian</t>
-  </si>
-  <si>
     <t>HSP PHP</t>
   </si>
   <si>
@@ -202,6 +199,15 @@
   </si>
   <si>
     <t>10/01/2026 au 31/03/2026</t>
+  </si>
+  <si>
+    <t>13/10/2025 au 08/05/2026</t>
+  </si>
+  <si>
+    <t>E-parapheur, dev appian</t>
+  </si>
+  <si>
+    <t>Simpliform, Appian</t>
   </si>
 </sst>
 </file>
@@ -747,15 +753,39 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -787,30 +817,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1122,66 +1128,66 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AQ81"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="1" customWidth="1"/>
-    <col min="3" max="8" width="18.7109375" style="1" customWidth="1"/>
-    <col min="9" max="43" width="11.42578125" customWidth="1"/>
-    <col min="44" max="16384" width="10.85546875" style="1"/>
+    <col min="1" max="1" width="70.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" style="1" customWidth="1"/>
+    <col min="3" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="43" width="11.44140625" customWidth="1"/>
+    <col min="44" max="16384" width="10.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="27"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="H1" s="25"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-    </row>
-    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+    </row>
+    <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="45" t="s">
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="46"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="33"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="42" t="s">
+    <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="12" t="s">
         <v>5</v>
       </c>
@@ -1192,23 +1198,23 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
+    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="25" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="42" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1230,9 +1236,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="35"/>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="35"/>
+      <c r="B7" s="43"/>
       <c r="C7" s="19" t="s">
         <v>16</v>
       </c>
@@ -1287,17 +1293,17 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="28" t="s">
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="30"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1334,7 +1340,7 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>23</v>
       </c>
@@ -1385,7 +1391,7 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>25</v>
       </c>
@@ -1446,7 +1452,7 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>27</v>
       </c>
@@ -1497,7 +1503,7 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>29</v>
       </c>
@@ -1554,7 +1560,7 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>31</v>
       </c>
@@ -1607,7 +1613,7 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>33</v>
       </c>
@@ -1660,7 +1666,7 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>35</v>
       </c>
@@ -1713,12 +1719,12 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="24"/>
       <c r="D16" s="24"/>
@@ -1766,12 +1772,12 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" s="24"/>
       <c r="D17" s="24"/>
@@ -1817,7 +1823,7 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="8"/>
       <c r="C18" s="14"/>
@@ -1862,17 +1868,17 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="31" t="s">
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A19" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="33"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1909,9 +1915,9 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="24" t="s">
@@ -1958,7 +1964,7 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
       <c r="C21" s="24"/>
       <c r="D21" s="14"/>
@@ -2002,7 +2008,7 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
       <c r="B22" s="8"/>
       <c r="C22" s="14"/>
@@ -2047,7 +2053,7 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
       <c r="B23" s="8"/>
       <c r="C23" s="14"/>
@@ -2092,7 +2098,7 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
       <c r="B24" s="8"/>
       <c r="C24" s="14"/>
@@ -2137,7 +2143,7 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
       <c r="B25" s="8"/>
       <c r="C25" s="14"/>
@@ -2182,7 +2188,7 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
       <c r="B26" s="8"/>
       <c r="C26" s="14"/>
@@ -2227,17 +2233,17 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="31" t="s">
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A27" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="33"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="41"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2274,15 +2280,27 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="9"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="14"/>
+    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>42</v>
+      </c>
       <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
+      <c r="E28" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>42</v>
+      </c>
       <c r="G28" s="14"/>
-      <c r="H28" s="15"/>
+      <c r="H28" s="24" t="s">
+        <v>42</v>
+      </c>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2319,7 +2337,7 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
       <c r="B29" s="8"/>
       <c r="C29" s="14"/>
@@ -2364,7 +2382,7 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
       <c r="B30" s="8"/>
       <c r="C30" s="14"/>
@@ -2411,7 +2429,7 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9"/>
       <c r="B31" s="8"/>
       <c r="C31" s="14"/>
@@ -2456,7 +2474,7 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="8"/>
       <c r="C32" s="14"/>
@@ -2501,7 +2519,7 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
       <c r="B33" s="8"/>
       <c r="C33" s="14"/>
@@ -2546,7 +2564,7 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="16"/>
@@ -2591,7 +2609,7 @@
       <c r="AP34"/>
       <c r="AQ34"/>
     </row>
-    <row r="35" spans="1:43" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:43" s="2" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="3"/>
       <c r="C35" s="4"/>
@@ -2636,59 +2654,54 @@
       <c r="AP35"/>
       <c r="AQ35"/>
     </row>
-    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="62" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="63" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="64" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="65" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="66" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="68" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="69" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="70" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="71" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="72" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="73" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="74" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="75" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="76" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="77" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="78" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="79" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="80" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2696,6 +2709,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2706,6 +2724,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ea44ee0b-87a5-495d-b2d6-65cb432e24f1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007C3C2D109AFBDD43B0E8E5DEFAF00640" ma:contentTypeVersion="6" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="776871779ab973961f405c98ce2ffbb9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ea44ee0b-87a5-495d-b2d6-65cb432e24f1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6736ff9efb90d459e07cecc95f77fd3b" ns3:_="">
     <xsd:import namespace="ea44ee0b-87a5-495d-b2d6-65cb432e24f1"/>
@@ -2861,14 +2887,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ea44ee0b-87a5-495d-b2d6-65cb432e24f1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2879,6 +2897,16 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76E9F743-2553-4538-B86E-9E9E949B7313}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ea44ee0b-87a5-495d-b2d6-65cb432e24f1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{932E8BFA-FE68-4273-8ADB-180549425F4E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2896,16 +2924,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76E9F743-2553-4538-B86E-9E9E949B7313}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ea44ee0b-87a5-495d-b2d6-65cb432e24f1"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AE36CC0-C123-4309-B645-BEFA7CB5FE5A}">
   <ds:schemaRefs>

--- a/assets/docs/E5-Tableau-de-synthese-Mateo.xlsx
+++ b/assets/docs/E5-Tableau-de-synthese-Mateo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\php\Portfolio\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C5D494-7858-400A-B23B-87BC1F422BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7405AF51-487E-4441-988C-3D4F27D2A42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="50">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -753,9 +753,48 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -778,45 +817,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1138,56 +1138,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="25"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="32" t="s">
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="33"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="46"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="44"/>
       <c r="F4" s="12" t="s">
         <v>5</v>
       </c>
@@ -1199,22 +1199,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="46"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1237,8 +1237,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35"/>
-      <c r="B7" s="43"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="19" t="s">
         <v>16</v>
       </c>
@@ -1294,16 +1294,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="30"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1726,16 +1726,24 @@
       <c r="B16" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
+      <c r="C16" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>42</v>
+      </c>
       <c r="F16" s="24" t="s">
         <v>42</v>
       </c>
       <c r="G16" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="24"/>
+      <c r="H16" s="24" t="s">
+        <v>42</v>
+      </c>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1779,14 +1787,24 @@
       <c r="B17" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
+      <c r="C17" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>42</v>
+      </c>
       <c r="F17" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
+      <c r="G17" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>42</v>
+      </c>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1869,16 +1887,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="41"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="33"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2234,16 +2252,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="39" t="s">
+      <c r="A27" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="41"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="33"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2702,6 +2720,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2709,11 +2732,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2724,14 +2742,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ea44ee0b-87a5-495d-b2d6-65cb432e24f1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007C3C2D109AFBDD43B0E8E5DEFAF00640" ma:contentTypeVersion="6" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="776871779ab973961f405c98ce2ffbb9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ea44ee0b-87a5-495d-b2d6-65cb432e24f1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6736ff9efb90d459e07cecc95f77fd3b" ns3:_="">
     <xsd:import namespace="ea44ee0b-87a5-495d-b2d6-65cb432e24f1"/>
@@ -2887,6 +2897,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ea44ee0b-87a5-495d-b2d6-65cb432e24f1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2897,16 +2915,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76E9F743-2553-4538-B86E-9E9E949B7313}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ea44ee0b-87a5-495d-b2d6-65cb432e24f1"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{932E8BFA-FE68-4273-8ADB-180549425F4E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2924,6 +2932,16 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76E9F743-2553-4538-B86E-9E9E949B7313}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ea44ee0b-87a5-495d-b2d6-65cb432e24f1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AE36CC0-C123-4309-B645-BEFA7CB5FE5A}">
   <ds:schemaRefs>
